--- a/fuction_ensemble/redes-ensemble-s/mse_sup_ensemble_100/content/results/metrics_15_7.xlsx
+++ b/fuction_ensemble/redes-ensemble-s/mse_sup_ensemble_100/content/results/metrics_15_7.xlsx
@@ -513,441 +513,441 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>model_15_7_10</t>
+          <t>model_15_7_12</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9737508042662341</v>
+        <v>0.9999634579513202</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8299244039462429</v>
+        <v>0.3175671747930876</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7791882898054137</v>
+        <v>0.9999118177697159</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8906618642917563</v>
+        <v>0.9997870581270399</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9360186337499748</v>
+        <v>0.9998451886616072</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1755284927381256</v>
+        <v>2.169293863062866e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.137296293937585</v>
+        <v>0.4051216046058956</v>
       </c>
       <c r="I2" t="n">
-        <v>0.07874143403851581</v>
+        <v>3.581949914306858e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>0.762053932831507</v>
+        <v>9.976136634456316e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>0.4203979109944825</v>
+        <v>6.7790200945237e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2775366104154802</v>
+        <v>0.001271154282580241</v>
       </c>
       <c r="M2" t="n">
-        <v>0.4189612067222043</v>
+        <v>0.00465756788792484</v>
       </c>
       <c r="N2" t="n">
-        <v>1.015365382868546</v>
+        <v>1.000067462243716</v>
       </c>
       <c r="O2" t="n">
-        <v>0.436797252661627</v>
+        <v>0.004855850195408477</v>
       </c>
       <c r="P2" t="n">
-        <v>133.4799077949393</v>
+        <v>95.47704751820312</v>
       </c>
       <c r="Q2" t="n">
-        <v>212.7068364113723</v>
+        <v>140.5754530383265</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>model_15_7_9</t>
+          <t>model_15_7_22</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9738439789468244</v>
+        <v>0.9999634579513202</v>
       </c>
       <c r="C3" t="n">
-        <v>0.829886390357797</v>
+        <v>0.3175671747930876</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7937187716037888</v>
+        <v>0.9999118177697159</v>
       </c>
       <c r="E3" t="n">
-        <v>0.899107880500823</v>
+        <v>0.9997870581270399</v>
       </c>
       <c r="F3" t="n">
-        <v>0.940892561892267</v>
+        <v>0.9998451886616072</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1749054332199881</v>
+        <v>2.169293863062866e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.137550490978559</v>
+        <v>0.4051216046058956</v>
       </c>
       <c r="I3" t="n">
-        <v>0.07355986566487138</v>
+        <v>3.581949914306858e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7031877391911425</v>
+        <v>9.976136634456316e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3883731305083983</v>
+        <v>6.7790200945237e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2934076432023445</v>
+        <v>0.001271154282580241</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4182169690722605</v>
+        <v>0.00465756788792484</v>
       </c>
       <c r="N3" t="n">
-        <v>1.015310841592103</v>
+        <v>1.000067462243716</v>
       </c>
       <c r="O3" t="n">
-        <v>0.4360213312741408</v>
+        <v>0.004855850195408477</v>
       </c>
       <c r="P3" t="n">
-        <v>133.4870196654349</v>
+        <v>95.47704751820312</v>
       </c>
       <c r="Q3" t="n">
-        <v>212.7139482818679</v>
+        <v>140.5754530383265</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>model_15_7_11</t>
+          <t>model_15_7_21</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9734943793145714</v>
+        <v>0.9999634579513202</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8297884123763323</v>
+        <v>0.3175671747930876</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7661474414086393</v>
+        <v>0.9999118177697159</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8828024537628911</v>
+        <v>0.9997870581270399</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9314964491198456</v>
+        <v>0.9998451886616072</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1772432075706218</v>
+        <v>2.169293863062866e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.138205670191761</v>
+        <v>0.4051216046058956</v>
       </c>
       <c r="I4" t="n">
-        <v>0.08339179928832977</v>
+        <v>3.581949914306858e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8168316612467857</v>
+        <v>9.976136634456316e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4501115148617166</v>
+        <v>6.7790200945237e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2632282108889326</v>
+        <v>0.001271154282580241</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4210026218096769</v>
+        <v>0.00465756788792484</v>
       </c>
       <c r="N4" t="n">
-        <v>1.015515485279275</v>
+        <v>1.000067462243716</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4389255750156851</v>
+        <v>0.004855850195408477</v>
       </c>
       <c r="P4" t="n">
-        <v>133.4604648709709</v>
+        <v>95.47704751820312</v>
       </c>
       <c r="Q4" t="n">
-        <v>212.6873934874039</v>
+        <v>140.5754530383265</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>model_15_7_8</t>
+          <t>model_15_7_20</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9737092919990741</v>
+        <v>0.9999634579513202</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8296087351945802</v>
+        <v>0.3175671747930876</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8098380693436438</v>
+        <v>0.9999118177697159</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9081348181092995</v>
+        <v>0.9997870581270399</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9461174654893356</v>
+        <v>0.9998451886616072</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1758060854597706</v>
+        <v>2.169293863062866e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>1.139407172333474</v>
+        <v>0.4051216046058956</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0678117256834751</v>
+        <v>3.581949914306858e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6402726980538027</v>
+        <v>9.976136634456316e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3540422200246859</v>
+        <v>6.7790200945237e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3110029422241042</v>
+        <v>0.001271154282580241</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4192923627491569</v>
+        <v>0.00465756788792484</v>
       </c>
       <c r="N5" t="n">
-        <v>1.015389682732249</v>
+        <v>1.000067462243716</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4371425066862344</v>
+        <v>0.004855850195408477</v>
       </c>
       <c r="P5" t="n">
-        <v>133.4767473570361</v>
+        <v>95.47704751820312</v>
       </c>
       <c r="Q5" t="n">
-        <v>212.7036759734692</v>
+        <v>140.5754530383265</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>model_15_7_12</t>
+          <t>model_15_7_19</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9731244991003652</v>
+        <v>0.9999634579513202</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8295291487680807</v>
+        <v>0.3175671747930876</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7544772413145837</v>
+        <v>0.9999118177697159</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8755219109162201</v>
+        <v>0.9997870581270399</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9273184060897989</v>
+        <v>0.9998451886616072</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1797165982661603</v>
+        <v>2.169293863062866e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.139939367133939</v>
+        <v>0.4051216046058956</v>
       </c>
       <c r="I6" t="n">
-        <v>0.08755339148881844</v>
+        <v>3.581949914306858e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8675748559566218</v>
+        <v>9.976136634456316e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4775638914648191</v>
+        <v>6.7790200945237e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2503278533262581</v>
+        <v>0.001271154282580241</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4239299449981804</v>
+        <v>0.00465756788792484</v>
       </c>
       <c r="N6" t="n">
-        <v>1.015732000526615</v>
+        <v>1.000067462243716</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4419775204127177</v>
+        <v>0.004855850195408477</v>
       </c>
       <c r="P6" t="n">
-        <v>133.4327482458483</v>
+        <v>95.47704751820312</v>
       </c>
       <c r="Q6" t="n">
-        <v>212.6596768622813</v>
+        <v>140.5754530383265</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>model_15_7_13</t>
+          <t>model_15_7_18</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9726794167952373</v>
+        <v>0.9999634579513202</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8291857111405891</v>
+        <v>0.3175671747930876</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7440519809208106</v>
+        <v>0.9999118177697159</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8688027909583202</v>
+        <v>0.9997870581270399</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9234719053556519</v>
+        <v>0.9998451886616072</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1826928656899668</v>
+        <v>2.169293863062866e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>1.142235936130359</v>
+        <v>0.4051216046058956</v>
       </c>
       <c r="I7" t="n">
-        <v>0.09127103831519026</v>
+        <v>3.581949914306858e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9144051019263107</v>
+        <v>9.976136634456316e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5028378261750444</v>
+        <v>6.7790200945237e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.238702352684141</v>
+        <v>0.001271154282580241</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4274258598750979</v>
+        <v>0.00465756788792484</v>
       </c>
       <c r="N7" t="n">
-        <v>1.015992536510105</v>
+        <v>1.000067462243716</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4456222636234869</v>
+        <v>0.004855850195408477</v>
       </c>
       <c r="P7" t="n">
-        <v>133.3998977313532</v>
+        <v>95.47704751820312</v>
       </c>
       <c r="Q7" t="n">
-        <v>212.6268263477863</v>
+        <v>140.5754530383265</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>model_15_7_7</t>
+          <t>model_15_7_17</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9732635215433021</v>
+        <v>0.9999634579513202</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8290067537579185</v>
+        <v>0.3175671747930876</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8276171097120906</v>
+        <v>0.9999118177697159</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9177179620427875</v>
+        <v>0.9997870581270399</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9516825360357914</v>
+        <v>0.9998451886616072</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1787869545501021</v>
+        <v>2.169293863062866e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>1.143432624972301</v>
+        <v>0.4051216046058956</v>
       </c>
       <c r="I8" t="n">
-        <v>0.06147172164471067</v>
+        <v>3.581949914306858e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5734810660573338</v>
+        <v>9.976136634456316e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3174761982375842</v>
+        <v>6.7790200945237e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3305178325449672</v>
+        <v>0.001271154282580241</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4228320642407599</v>
+        <v>0.00465756788792484</v>
       </c>
       <c r="N8" t="n">
-        <v>1.015650621535628</v>
+        <v>1.000067462243716</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4408329005985272</v>
+        <v>0.004855850195408477</v>
       </c>
       <c r="P8" t="n">
-        <v>133.4431207600674</v>
+        <v>95.47704751820312</v>
       </c>
       <c r="Q8" t="n">
-        <v>212.6700493765004</v>
+        <v>140.5754530383265</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>model_15_7_14</t>
+          <t>model_15_7_16</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9721882734952496</v>
+        <v>0.9999634579513202</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8287879399861852</v>
+        <v>0.3175671747930876</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7347552408880509</v>
+        <v>0.9999118177697159</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8626211283191382</v>
+        <v>0.9997870581270399</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9199410010665472</v>
+        <v>0.9998451886616072</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1859771431984913</v>
+        <v>2.169293863062866e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>1.144895833671426</v>
+        <v>0.4051216046058956</v>
       </c>
       <c r="I9" t="n">
-        <v>0.09458625489232599</v>
+        <v>3.581949914306858e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9574894319737556</v>
+        <v>9.976136634456316e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5260380932850091</v>
+        <v>6.7790200945237e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2282333234787442</v>
+        <v>0.001271154282580241</v>
       </c>
       <c r="M9" t="n">
-        <v>0.4312506732730876</v>
+        <v>0.00465756788792484</v>
       </c>
       <c r="N9" t="n">
-        <v>1.016280035027171</v>
+        <v>1.000067462243716</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4496099072462842</v>
+        <v>0.004855850195408477</v>
       </c>
       <c r="P9" t="n">
-        <v>133.3642629976993</v>
+        <v>95.47704751820312</v>
       </c>
       <c r="Q9" t="n">
-        <v>212.5911916141324</v>
+        <v>140.5754530383265</v>
       </c>
     </row>
     <row r="10">
@@ -957,877 +957,877 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9716731159088202</v>
+        <v>0.9999634579513202</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8283584431290901</v>
+        <v>0.3175671747930876</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7264685368259653</v>
+        <v>0.9999118177697159</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8569492300933559</v>
+        <v>0.9997870581270399</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9167079798620632</v>
+        <v>0.9998451886616072</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1894220043510271</v>
+        <v>2.169293863062866e-05</v>
       </c>
       <c r="H10" t="n">
-        <v>1.147767881132472</v>
+        <v>0.4051216046058956</v>
       </c>
       <c r="I10" t="n">
-        <v>0.09754129274211391</v>
+        <v>3.581949914306858e-05</v>
       </c>
       <c r="J10" t="n">
-        <v>0.9970208573230138</v>
+        <v>9.976136634456316e-05</v>
       </c>
       <c r="K10" t="n">
-        <v>0.5472810807394289</v>
+        <v>6.7790200945237e-05</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2187915372172938</v>
+        <v>0.001271154282580241</v>
       </c>
       <c r="M10" t="n">
-        <v>0.435226382875656</v>
+        <v>0.00465756788792484</v>
       </c>
       <c r="N10" t="n">
-        <v>1.01658159068752</v>
+        <v>1.000067462243716</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4537548710374875</v>
+        <v>0.004855850195408477</v>
       </c>
       <c r="P10" t="n">
-        <v>133.3275558514455</v>
+        <v>95.47704751820312</v>
       </c>
       <c r="Q10" t="n">
-        <v>212.5544844678786</v>
+        <v>140.5754530383265</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>model_15_7_6</t>
+          <t>model_15_7_14</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9723995424863029</v>
+        <v>0.9999634579513202</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8279716600798495</v>
+        <v>0.3175671747930876</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8470682468807782</v>
+        <v>0.9999118177697159</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9278059354276513</v>
+        <v>0.9997870581270399</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9575606107298744</v>
+        <v>0.9998451886616072</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1845643864825133</v>
+        <v>2.169293863062866e-05</v>
       </c>
       <c r="H11" t="n">
-        <v>1.150354301163717</v>
+        <v>0.4051216046058956</v>
       </c>
       <c r="I11" t="n">
-        <v>0.05453544805218861</v>
+        <v>3.581949914306858e-05</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5031709245642648</v>
+        <v>9.976136634456316e-05</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2788535418784595</v>
+        <v>6.7790200945237e-05</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3521434647556352</v>
+        <v>0.001271154282580241</v>
       </c>
       <c r="M11" t="n">
-        <v>0.4296095744772378</v>
+        <v>0.00465756788792484</v>
       </c>
       <c r="N11" t="n">
-        <v>1.016156365373871</v>
+        <v>1.000067462243716</v>
       </c>
       <c r="O11" t="n">
-        <v>0.4478989434771523</v>
+        <v>0.004855850195408477</v>
       </c>
       <c r="P11" t="n">
-        <v>133.3795137963106</v>
+        <v>95.47704751820312</v>
       </c>
       <c r="Q11" t="n">
-        <v>212.6064424127436</v>
+        <v>140.5754530383265</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>model_15_7_16</t>
+          <t>model_15_7_13</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9711504027200981</v>
+        <v>0.9999634579513202</v>
       </c>
       <c r="C12" t="n">
-        <v>0.827914298549381</v>
+        <v>0.3175671747930876</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7190864413979376</v>
+        <v>0.9999118177697159</v>
       </c>
       <c r="E12" t="n">
-        <v>0.8517572142357408</v>
+        <v>0.9997870581270399</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9137539827378834</v>
+        <v>0.9998451886616072</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1929173898508847</v>
+        <v>2.169293863062866e-05</v>
       </c>
       <c r="H12" t="n">
-        <v>1.150737877982085</v>
+        <v>0.4051216046058956</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1001737472423749</v>
+        <v>3.581949914306858e-05</v>
       </c>
       <c r="J12" t="n">
-        <v>1.033207646845169</v>
+        <v>9.976136634456316e-05</v>
       </c>
       <c r="K12" t="n">
-        <v>0.5666907040856393</v>
+        <v>6.7790200945237e-05</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2102895226710625</v>
+        <v>0.001271154282580241</v>
       </c>
       <c r="M12" t="n">
-        <v>0.4392236216904605</v>
+        <v>0.00465756788792484</v>
       </c>
       <c r="N12" t="n">
-        <v>1.016887569139455</v>
+        <v>1.000067462243716</v>
       </c>
       <c r="O12" t="n">
-        <v>0.4579222805840632</v>
+        <v>0.004855850195408477</v>
       </c>
       <c r="P12" t="n">
-        <v>133.2909864271395</v>
+        <v>95.47704751820312</v>
       </c>
       <c r="Q12" t="n">
-        <v>212.5179150435725</v>
+        <v>140.5754530383265</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>model_15_7_17</t>
+          <t>model_15_7_23</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.970632139627113</v>
+        <v>0.9999634579513202</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8274680082568532</v>
+        <v>0.3175671747930876</v>
       </c>
       <c r="D13" t="n">
-        <v>0.712506673536021</v>
+        <v>0.9999118177697159</v>
       </c>
       <c r="E13" t="n">
-        <v>0.847013686682766</v>
+        <v>0.9997870581270399</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9110596251919604</v>
+        <v>0.9998451886616072</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1963830175400581</v>
+        <v>2.169293863062866e-05</v>
       </c>
       <c r="H13" t="n">
-        <v>1.153722223223196</v>
+        <v>0.4051216046058956</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1025200918118332</v>
+        <v>3.581949914306858e-05</v>
       </c>
       <c r="J13" t="n">
-        <v>1.066268607724224</v>
+        <v>9.976136634456316e-05</v>
       </c>
       <c r="K13" t="n">
-        <v>0.5843943317223468</v>
+        <v>6.7790200945237e-05</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2026280481418588</v>
+        <v>0.001271154282580241</v>
       </c>
       <c r="M13" t="n">
-        <v>0.4431512355167908</v>
+        <v>0.00465756788792484</v>
       </c>
       <c r="N13" t="n">
-        <v>1.0171909426573</v>
+        <v>1.000067462243716</v>
       </c>
       <c r="O13" t="n">
-        <v>0.4620171010622618</v>
+        <v>0.004855850195408477</v>
       </c>
       <c r="P13" t="n">
-        <v>133.2553767110748</v>
+        <v>95.47704751820312</v>
       </c>
       <c r="Q13" t="n">
-        <v>212.4823053275078</v>
+        <v>140.5754530383265</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>model_15_7_18</t>
+          <t>model_15_7_24</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9701270234842553</v>
+        <v>0.9999634579513202</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8270287949714609</v>
+        <v>0.3175671747930876</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7066476432365293</v>
+        <v>0.9999118177697159</v>
       </c>
       <c r="E14" t="n">
-        <v>0.842686865691463</v>
+        <v>0.9997870581270399</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9086058247411384</v>
+        <v>0.9998451886616072</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1997607315131938</v>
+        <v>2.169293863062866e-05</v>
       </c>
       <c r="H14" t="n">
-        <v>1.156659244485006</v>
+        <v>0.4051216046058956</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1046094214377418</v>
+        <v>3.581949914306858e-05</v>
       </c>
       <c r="J14" t="n">
-        <v>1.09642524915333</v>
+        <v>9.976136634456316e-05</v>
       </c>
       <c r="K14" t="n">
-        <v>0.6005173475937451</v>
+        <v>6.7790200945237e-05</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1957302220648413</v>
+        <v>0.001271154282580241</v>
       </c>
       <c r="M14" t="n">
-        <v>0.4469460051428962</v>
+        <v>0.00465756788792484</v>
       </c>
       <c r="N14" t="n">
-        <v>1.01748662039946</v>
+        <v>1.000067462243716</v>
       </c>
       <c r="O14" t="n">
-        <v>0.4659734218876066</v>
+        <v>0.004855850195408477</v>
       </c>
       <c r="P14" t="n">
-        <v>133.221269942114</v>
+        <v>95.47704751820312</v>
       </c>
       <c r="Q14" t="n">
-        <v>212.4481985585471</v>
+        <v>140.5754530383265</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>model_15_7_19</t>
+          <t>model_15_7_10</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9696412346968204</v>
+        <v>0.9999634579513202</v>
       </c>
       <c r="C15" t="n">
-        <v>0.8266032145684146</v>
+        <v>0.3175671747930876</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7014249125054172</v>
+        <v>0.9999118177697159</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8387470285418482</v>
+        <v>0.9997870581270399</v>
       </c>
       <c r="F15" t="n">
-        <v>0.906374541042229</v>
+        <v>0.9998451886616072</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2030092033716228</v>
+        <v>2.169293863062866e-05</v>
       </c>
       <c r="H15" t="n">
-        <v>1.159505102599794</v>
+        <v>0.4051216046058956</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1064718467004346</v>
+        <v>3.581949914306858e-05</v>
       </c>
       <c r="J15" t="n">
-        <v>1.123884729554487</v>
+        <v>9.976136634456316e-05</v>
       </c>
       <c r="K15" t="n">
-        <v>0.6151782881274608</v>
+        <v>6.7790200945237e-05</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1895171198753799</v>
+        <v>0.001271154282580241</v>
       </c>
       <c r="M15" t="n">
-        <v>0.4505654262941429</v>
+        <v>0.00465756788792484</v>
       </c>
       <c r="N15" t="n">
-        <v>1.017770984567715</v>
+        <v>1.000067462243716</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4697469292904966</v>
+        <v>0.004855850195408477</v>
       </c>
       <c r="P15" t="n">
-        <v>133.189007928324</v>
+        <v>95.47704751820312</v>
       </c>
       <c r="Q15" t="n">
-        <v>212.415936544757</v>
+        <v>140.5754530383265</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>model_15_7_5</t>
+          <t>model_15_7_9</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9709798419003695</v>
+        <v>0.9999634579513202</v>
       </c>
       <c r="C16" t="n">
-        <v>0.8263639733154442</v>
+        <v>0.3175671747930876</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8681128752541089</v>
+        <v>0.9999118177697159</v>
       </c>
       <c r="E16" t="n">
-        <v>0.938310168183856</v>
+        <v>0.9997870581270399</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9637028145522266</v>
+        <v>0.9998451886616072</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1940579308377709</v>
+        <v>2.169293863062866e-05</v>
       </c>
       <c r="H16" t="n">
-        <v>1.161104909960011</v>
+        <v>0.4051216046058956</v>
       </c>
       <c r="I16" t="n">
-        <v>0.04703093565353267</v>
+        <v>3.581949914306858e-05</v>
       </c>
       <c r="J16" t="n">
-        <v>0.4299595804034025</v>
+        <v>9.976136634456316e-05</v>
       </c>
       <c r="K16" t="n">
-        <v>0.2384953906359768</v>
+        <v>6.7790200945237e-05</v>
       </c>
       <c r="L16" t="n">
-        <v>0.3761166951657918</v>
+        <v>0.001271154282580241</v>
       </c>
       <c r="M16" t="n">
-        <v>0.4405200685982091</v>
+        <v>0.00465756788792484</v>
       </c>
       <c r="N16" t="n">
-        <v>1.016987409619296</v>
+        <v>1.000067462243716</v>
       </c>
       <c r="O16" t="n">
-        <v>0.4592739199206898</v>
+        <v>0.004855850195408477</v>
       </c>
       <c r="P16" t="n">
-        <v>133.2791971038577</v>
+        <v>95.47704751820312</v>
       </c>
       <c r="Q16" t="n">
-        <v>212.5061257202907</v>
+        <v>140.5754530383265</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>model_15_7_20</t>
+          <t>model_15_7_8</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9691787296777884</v>
+        <v>0.9999634579513202</v>
       </c>
       <c r="C17" t="n">
-        <v>0.8261956856260235</v>
+        <v>0.3175671747930876</v>
       </c>
       <c r="D17" t="n">
-        <v>0.696766468142862</v>
+        <v>0.9999118177697159</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8351638166007784</v>
+        <v>0.9997870581270399</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9043477502276289</v>
+        <v>0.9998451886616072</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2061019765635294</v>
+        <v>2.169293863062866e-05</v>
       </c>
       <c r="H17" t="n">
-        <v>1.162230250514061</v>
+        <v>0.4051216046058956</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1081330474998531</v>
+        <v>3.581949914306858e-05</v>
       </c>
       <c r="J17" t="n">
-        <v>1.148858639473231</v>
+        <v>9.976136634456316e-05</v>
       </c>
       <c r="K17" t="n">
-        <v>0.6284955814961433</v>
+        <v>6.7790200945237e-05</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1839180194158041</v>
+        <v>0.001271154282580241</v>
       </c>
       <c r="M17" t="n">
-        <v>0.4539845554240027</v>
+        <v>0.00465756788792484</v>
       </c>
       <c r="N17" t="n">
-        <v>1.018041719213002</v>
+        <v>1.000067462243716</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4733116178259875</v>
+        <v>0.004855850195408477</v>
       </c>
       <c r="P17" t="n">
-        <v>133.1587684016372</v>
+        <v>95.47704751820312</v>
       </c>
       <c r="Q17" t="n">
-        <v>212.3856970180703</v>
+        <v>140.5754530383265</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>model_15_7_21</t>
+          <t>model_15_7_7</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9687419808609962</v>
+        <v>0.9999634579513202</v>
       </c>
       <c r="C18" t="n">
-        <v>0.825809101397039</v>
+        <v>0.3175671747930876</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6926121804369874</v>
+        <v>0.9999118177697159</v>
       </c>
       <c r="E18" t="n">
-        <v>0.831908433749585</v>
+        <v>0.9997870581270399</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9025085148373803</v>
+        <v>0.9998451886616072</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2090225179124624</v>
+        <v>2.169293863062866e-05</v>
       </c>
       <c r="H18" t="n">
-        <v>1.164815341033337</v>
+        <v>0.4051216046058956</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1096144660853117</v>
+        <v>3.581949914306858e-05</v>
       </c>
       <c r="J18" t="n">
-        <v>1.171547679198985</v>
+        <v>9.976136634456316e-05</v>
       </c>
       <c r="K18" t="n">
-        <v>0.6405805174893215</v>
+        <v>6.7790200945237e-05</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1788777974885833</v>
+        <v>0.001271154282580241</v>
       </c>
       <c r="M18" t="n">
-        <v>0.4571898051274355</v>
+        <v>0.00465756788792484</v>
       </c>
       <c r="N18" t="n">
-        <v>1.018297377056978</v>
+        <v>1.000067462243716</v>
       </c>
       <c r="O18" t="n">
-        <v>0.476653321645077</v>
+        <v>0.004855850195408477</v>
       </c>
       <c r="P18" t="n">
-        <v>133.1306265832261</v>
+        <v>95.47704751820312</v>
       </c>
       <c r="Q18" t="n">
-        <v>212.3575551996591</v>
+        <v>140.5754530383265</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>model_15_7_22</t>
+          <t>model_15_7_11</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9683324048712825</v>
+        <v>0.9999634579513202</v>
       </c>
       <c r="C19" t="n">
-        <v>0.825445230560363</v>
+        <v>0.3175671747930876</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6889052174859516</v>
+        <v>0.9999118177697159</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8289543576524427</v>
+        <v>0.9997870581270399</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9008410922472027</v>
+        <v>0.9998451886616072</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2117613544416018</v>
+        <v>2.169293863062866e-05</v>
       </c>
       <c r="H19" t="n">
-        <v>1.167248546993661</v>
+        <v>0.4051216046058956</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1109363687073918</v>
+        <v>3.581949914306858e-05</v>
       </c>
       <c r="J19" t="n">
-        <v>1.192136701438378</v>
+        <v>9.976136634456316e-05</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6515365350728849</v>
+        <v>6.7790200945237e-05</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1743412103416619</v>
+        <v>0.001271154282580241</v>
       </c>
       <c r="M19" t="n">
-        <v>0.4601753518405802</v>
+        <v>0.00465756788792484</v>
       </c>
       <c r="N19" t="n">
-        <v>1.018537128855835</v>
+        <v>1.000067462243716</v>
       </c>
       <c r="O19" t="n">
-        <v>0.479765969262734</v>
+        <v>0.004855850195408477</v>
       </c>
       <c r="P19" t="n">
-        <v>133.1045906499347</v>
+        <v>95.47704751820312</v>
       </c>
       <c r="Q19" t="n">
-        <v>212.3315192663678</v>
+        <v>140.5754530383265</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>model_15_7_23</t>
+          <t>model_15_7_6</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9679503580273567</v>
+        <v>0.9999634571396949</v>
       </c>
       <c r="C20" t="n">
-        <v>0.8251047712132783</v>
+        <v>0.3175671392652086</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6855950929183661</v>
+        <v>0.9999118167076799</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8262757051286315</v>
+        <v>0.9997870526199077</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8993306392117781</v>
+        <v>0.9998451857156077</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2143161034460976</v>
+        <v>2.169342044643348e-05</v>
       </c>
       <c r="H20" t="n">
-        <v>1.169525200215287</v>
+        <v>0.4051216256967793</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1121167588011423</v>
+        <v>3.581993054065272e-05</v>
       </c>
       <c r="J20" t="n">
-        <v>1.210806104179122</v>
+        <v>9.97639463868525e-05</v>
       </c>
       <c r="K20" t="n">
-        <v>0.6614611637259574</v>
+        <v>6.779149096638166e-05</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1702510243183006</v>
+        <v>0.001271171296009051</v>
       </c>
       <c r="M20" t="n">
-        <v>0.4629428727673617</v>
+        <v>0.004657619611607789</v>
       </c>
       <c r="N20" t="n">
-        <v>1.018760766032767</v>
+        <v>1.000067463742102</v>
       </c>
       <c r="O20" t="n">
-        <v>0.4826513092849267</v>
+        <v>0.004855904121075691</v>
       </c>
       <c r="P20" t="n">
-        <v>133.0806064698406</v>
+        <v>95.47700309725468</v>
       </c>
       <c r="Q20" t="n">
-        <v>212.3075350862737</v>
+        <v>140.5754086173781</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>model_15_7_24</t>
+          <t>model_15_7_5</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9675956281218507</v>
+        <v>0.9999634571396937</v>
       </c>
       <c r="C21" t="n">
-        <v>0.8247879024975949</v>
+        <v>0.3175671276982742</v>
       </c>
       <c r="D21" t="n">
-        <v>0.6826364838573322</v>
+        <v>0.9999118167076799</v>
       </c>
       <c r="E21" t="n">
-        <v>0.8238487451542096</v>
+        <v>0.9997870526199077</v>
       </c>
       <c r="F21" t="n">
-        <v>0.897963131918091</v>
+        <v>0.9998451857156077</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2166881839575968</v>
+        <v>2.169342044722211e-05</v>
       </c>
       <c r="H21" t="n">
-        <v>1.171644102776108</v>
+        <v>0.4051216325634113</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1131717984999874</v>
+        <v>3.581993054065272e-05</v>
       </c>
       <c r="J21" t="n">
-        <v>1.227721285523242</v>
+        <v>9.97639463868525e-05</v>
       </c>
       <c r="K21" t="n">
-        <v>0.6704465487408574</v>
+        <v>6.779149096638166e-05</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1665751018345841</v>
+        <v>0.001271174199013743</v>
       </c>
       <c r="M21" t="n">
-        <v>0.4654977808299378</v>
+        <v>0.004657619611692448</v>
       </c>
       <c r="N21" t="n">
-        <v>1.018968412806722</v>
+        <v>1.000067463742104</v>
       </c>
       <c r="O21" t="n">
-        <v>0.4853149850731154</v>
+        <v>0.004855904121163954</v>
       </c>
       <c r="P21" t="n">
-        <v>133.058591798236</v>
+        <v>95.47700309718198</v>
       </c>
       <c r="Q21" t="n">
-        <v>212.2855204146691</v>
+        <v>140.5754086173054</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>model_15_7_4</t>
+          <t>model_15_7_3</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9688283079844909</v>
+        <v>0.999963457139657</v>
       </c>
       <c r="C22" t="n">
-        <v>0.8240050425201302</v>
+        <v>0.317567126929479</v>
       </c>
       <c r="D22" t="n">
-        <v>0.8905252913801719</v>
+        <v>0.9999118167076799</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9490923921775491</v>
+        <v>0.9997870526199077</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9700295296247124</v>
+        <v>0.9998451857156077</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2084452480401532</v>
+        <v>2.169342046903538e-05</v>
       </c>
       <c r="H22" t="n">
-        <v>1.176879091050154</v>
+        <v>0.4051216330198014</v>
       </c>
       <c r="I22" t="n">
-        <v>0.039038670277394</v>
+        <v>3.581993054065272e-05</v>
       </c>
       <c r="J22" t="n">
-        <v>0.3548107208966954</v>
+        <v>9.97639463868525e-05</v>
       </c>
       <c r="K22" t="n">
-        <v>0.196924884161691</v>
+        <v>6.779149096638166e-05</v>
       </c>
       <c r="L22" t="n">
-        <v>0.4026884251242598</v>
+        <v>0.001271175373303618</v>
       </c>
       <c r="M22" t="n">
-        <v>0.4565580445465321</v>
+        <v>0.004657619614034124</v>
       </c>
       <c r="N22" t="n">
-        <v>1.018246844106639</v>
+        <v>1.000067463742172</v>
       </c>
       <c r="O22" t="n">
-        <v>0.4759946657083199</v>
+        <v>0.004855904123605321</v>
       </c>
       <c r="P22" t="n">
-        <v>133.1361577431126</v>
+        <v>95.47700309517093</v>
       </c>
       <c r="Q22" t="n">
-        <v>212.3630863595457</v>
+        <v>140.5754086152944</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>model_15_7_3</t>
+          <t>model_15_7_1</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9657195601523733</v>
+        <v>0.9999634576040884</v>
       </c>
       <c r="C23" t="n">
-        <v>0.8206664234273392</v>
+        <v>0.3175671268257518</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9138715597385887</v>
+        <v>0.9999118177697159</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9599471841788036</v>
+        <v>0.9997870553772775</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9764201105547552</v>
+        <v>0.9998451872274657</v>
       </c>
       <c r="G23" t="n">
-        <v>0.2292334591079914</v>
+        <v>2.169314476240711e-05</v>
       </c>
       <c r="H23" t="n">
-        <v>1.199204452296575</v>
+        <v>0.4051216330813782</v>
       </c>
       <c r="I23" t="n">
-        <v>0.03071339328746541</v>
+        <v>3.581949914306858e-05</v>
       </c>
       <c r="J23" t="n">
-        <v>0.2791560841952186</v>
+        <v>9.976265458370676e-05</v>
       </c>
       <c r="K23" t="n">
-        <v>0.154934738741342</v>
+        <v>6.779082894015301e-05</v>
       </c>
       <c r="L23" t="n">
-        <v>0.4321393277512135</v>
+        <v>0.001271176398555209</v>
       </c>
       <c r="M23" t="n">
-        <v>0.4787833112254347</v>
+        <v>0.004657590016565124</v>
       </c>
       <c r="N23" t="n">
-        <v>1.020066598935196</v>
+        <v>1.00006746288476</v>
       </c>
       <c r="O23" t="n">
-        <v>0.4991661080023879</v>
+        <v>0.00485587326611079</v>
       </c>
       <c r="P23" t="n">
-        <v>132.9460286452987</v>
+        <v>95.47702851378858</v>
       </c>
       <c r="Q23" t="n">
-        <v>212.1729572617317</v>
+        <v>140.575434033912</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>model_15_7_2</t>
+          <t>model_15_7_4</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9613653432976141</v>
+        <v>0.9999634571396694</v>
       </c>
       <c r="C24" t="n">
-        <v>0.8160562038271776</v>
+        <v>0.3175671251509943</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9374075979879462</v>
+        <v>0.9999118167076799</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9705766679698445</v>
+        <v>0.9997870526199077</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9826962812773805</v>
+        <v>0.9998451857156077</v>
       </c>
       <c r="G24" t="n">
-        <v>0.2583501272650907</v>
+        <v>2.169342046165502e-05</v>
       </c>
       <c r="H24" t="n">
-        <v>1.230033011990965</v>
+        <v>0.4051216340755867</v>
       </c>
       <c r="I24" t="n">
-        <v>0.02232044437317725</v>
+        <v>3.581993054065272e-05</v>
       </c>
       <c r="J24" t="n">
-        <v>0.2050717779788951</v>
+        <v>9.97639463868525e-05</v>
       </c>
       <c r="K24" t="n">
-        <v>0.1136963405094912</v>
+        <v>6.779149096638166e-05</v>
       </c>
       <c r="L24" t="n">
-        <v>0.4647711873502648</v>
+        <v>0.00127117766393637</v>
       </c>
       <c r="M24" t="n">
-        <v>0.5082815433055686</v>
+        <v>0.004657619613241835</v>
       </c>
       <c r="N24" t="n">
-        <v>1.022615408801397</v>
+        <v>1.000067463742149</v>
       </c>
       <c r="O24" t="n">
-        <v>0.5299201408919315</v>
+        <v>0.004855904122779302</v>
       </c>
       <c r="P24" t="n">
-        <v>132.7068790632836</v>
+        <v>95.47700309585134</v>
       </c>
       <c r="Q24" t="n">
-        <v>211.9338076797166</v>
+        <v>140.5754086159748</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>model_15_7_1</t>
+          <t>model_15_7_2</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9553970350866502</v>
+        <v>0.9999634571883476</v>
       </c>
       <c r="C25" t="n">
-        <v>0.8098016006673674</v>
+        <v>0.3175671245584765</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9599613750177554</v>
+        <v>0.9999118167076799</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9805600190598547</v>
+        <v>0.9997870530055875</v>
       </c>
       <c r="F25" t="n">
-        <v>0.988603162081712</v>
+        <v>0.9998451859219323</v>
       </c>
       <c r="G25" t="n">
-        <v>0.2982602317533394</v>
+        <v>2.169339156418433e-05</v>
       </c>
       <c r="H25" t="n">
-        <v>1.271857572120414</v>
+        <v>0.4051216344273308</v>
       </c>
       <c r="I25" t="n">
-        <v>0.01427776971272959</v>
+        <v>3.581993054065272e-05</v>
       </c>
       <c r="J25" t="n">
-        <v>0.1354908224257416</v>
+        <v>9.976376569932775e-05</v>
       </c>
       <c r="K25" t="n">
-        <v>0.0748844098462671</v>
+        <v>6.779140061906658e-05</v>
       </c>
       <c r="L25" t="n">
-        <v>0.5009609024250939</v>
+        <v>0.001271176442339468</v>
       </c>
       <c r="M25" t="n">
-        <v>0.5461320643885867</v>
+        <v>0.004657616511069189</v>
       </c>
       <c r="N25" t="n">
-        <v>1.026109052632205</v>
+        <v>1.000067463652281</v>
       </c>
       <c r="O25" t="n">
-        <v>0.5693820370188339</v>
+        <v>0.004855900888540744</v>
       </c>
       <c r="P25" t="n">
-        <v>132.4195778252599</v>
+        <v>95.47700576002227</v>
       </c>
       <c r="Q25" t="n">
-        <v>211.646506441693</v>
+        <v>140.5754112801457</v>
       </c>
     </row>
     <row r="26">
@@ -1837,52 +1837,52 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.9473440397714143</v>
+        <v>0.99996346149549</v>
       </c>
       <c r="C26" t="n">
-        <v>0.8014267663651036</v>
+        <v>0.3175670990354283</v>
       </c>
       <c r="D26" t="n">
-        <v>0.97976994335417</v>
+        <v>0.9999118323976419</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9893113274387146</v>
+        <v>0.9997870735142609</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9937821134734177</v>
+        <v>0.9998452031481758</v>
       </c>
       <c r="G26" t="n">
-        <v>0.3521106485069551</v>
+        <v>2.169083465838788e-05</v>
       </c>
       <c r="H26" t="n">
-        <v>1.327860127662219</v>
+        <v>0.4051216495789147</v>
       </c>
       <c r="I26" t="n">
-        <v>0.007214036201111391</v>
+        <v>3.581355729993854e-05</v>
       </c>
       <c r="J26" t="n">
-        <v>0.07449683414952928</v>
+        <v>9.975415756894426e-05</v>
       </c>
       <c r="K26" t="n">
-        <v>0.04085543432069005</v>
+        <v>6.77838574344414e-05</v>
       </c>
       <c r="L26" t="n">
-        <v>0.5410988914252188</v>
+        <v>0.0012711438213095</v>
       </c>
       <c r="M26" t="n">
-        <v>0.5933891206509899</v>
+        <v>0.004657342016471184</v>
       </c>
       <c r="N26" t="n">
-        <v>1.030823001109416</v>
+        <v>1.000067455700634</v>
       </c>
       <c r="O26" t="n">
-        <v>0.61865092400192</v>
+        <v>0.00485561470813942</v>
       </c>
       <c r="P26" t="n">
-        <v>132.0876196208599</v>
+        <v>95.4772415052248</v>
       </c>
       <c r="Q26" t="n">
-        <v>211.3145482372929</v>
+        <v>140.5756470253482</v>
       </c>
     </row>
   </sheetData>
